--- a/invoice_agent/invoice_template.xlsx
+++ b/invoice_agent/invoice_template.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="請求データ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="顧客マスタ" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -189,6 +190,31 @@
 </comments>
 </file>
 
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>invoice_agent</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>「請求データ」シートの顧客名と一致させる</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>請求書右上に載る担当者名</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>請求書の本文。「下記の通り、ご請求申し上げます。」か「下記の通り、ご注文を受付致します。」など、顧客ごとに決まった文言があれば入力（空欄ならご請求申し上げます。になる）</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -633,4 +659,58 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>顧客名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>請求文言</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>（記入例）A社</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>辰巳</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>下記の通り、ご請求申し上げます。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>
--- a/invoice_agent/invoice_template.xlsx
+++ b/invoice_agent/invoice_template.xlsx
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -709,6 +709,19 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Vastra</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>竹田</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/invoice_agent/invoice_template.xlsx
+++ b/invoice_agent/invoice_template.xlsx
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -691,6 +691,11 @@
           <t>請求文言</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>敬称</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -708,6 +713,11 @@
           <t>下記の通り、ご請求申し上げます。</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>御中</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -720,7 +730,28 @@
           <t>竹田</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>御中</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>大谷　晃巨</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>竹田</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>様</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
